--- a/data/export/survey.xlsx
+++ b/data/export/survey.xlsx
@@ -420,17 +420,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -479,6 +479,207 @@
         <is>
           <t>TG id</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Недоответивший Петров</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>@half</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>не закончил</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>29.09.2026 16:06</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>9899</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Опрошенный 0 Иванов</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>@poll0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Мужской</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Не актуально</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>полностью</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>29.09.2026 16:06</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Опрошенный 1 Иванов</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>@poll1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Мужской</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Не актуально</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>полностью</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>29.09.2026 16:06</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>9801</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Опрошенный 2 Иванов</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>@poll2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Актуально</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>полностью</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>29.09.2026 16:06</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>9802</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Опрошенный 3 Иванов</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>@poll3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Актуально</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>полностью</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>29.09.2026 16:06</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>9803</v>
       </c>
     </row>
   </sheetData>
@@ -518,7 +719,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -528,7 +729,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -538,7 +739,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -548,7 +749,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -562,7 +763,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +773,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -586,7 +787,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -596,7 +797,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -654,17 +855,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -675,17 +876,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
